--- a/src/main/resources/espacios/Software/PENDIENTE_0 - Scala.xlsx
+++ b/src/main/resources/espacios/Software/PENDIENTE_0 - Scala.xlsx
@@ -5,17 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sheet9" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="0 Scala" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="1 Scala" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="2 Scala" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="3 Scala" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="4 Scala" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="5 Scala" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="6 Scala" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="7 Scala" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Fuente" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="485">
   <si>
     <t xml:space="preserve">How does Scala compare to Java?</t>
   </si>
@@ -39,10 +39,16 @@
     <t xml:space="preserve">Scala type inference reduces boilerplate code. Its Akka framework simplifies writing concurrent and parallel applications compared to Java general threading model.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Is it Difficult to Learn Scala?Scala can be challenging for beginners due to its advanced features and different paradigms. However, those with a background in Java and functional programming languages might find it easier to pick up. With practice and the right resources, anyone can learn Scala.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. What are some common use cases of Scala?There are various applications of the Scala programming language, some of which are listed below −</t>
+    <t xml:space="preserve">Is it Difficult to Learn Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scala can be challenging for beginners due to its advanced features and different paradigms. However, those with a background in Java and functional programming languages might find it easier to pick up. With practice and the right resources, anyone can learn Scala.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are some common use cases of Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are various applications of the Scala programming language, some of which are listed below −</t>
   </si>
   <si>
     <t xml:space="preserve">Data processing with frameworks like Apache SparkWeb development using Play FrameworkConcurrent and parallel programmingBuilding robust backend systemsFinancial applications4. How can I get started with Scala?To get started with Scala −</t>
@@ -54,10 +60,16 @@
     <t xml:space="preserve">Apache Spark − For large-scale data processing.Akka − For building concurrent and distributed systems.Play Framework − For web development.Scalatra − A simple web framework similar to Sinatra.Cats − For functional programming abstractions.</t>
   </si>
   <si>
-    <t xml:space="preserve">What are the IDEs that support Scala?IntelliJ IDEA − Comprehensive support for Scala with a dedicated plugin.Visual Studio Code − Lightweight and customizable with Scala plugins.Eclipse − With the Scala IDE plugin.Atom − With Scala plugins for syntax highlighting and code completion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> How does Scala handle concurrency and parallelism?You can use various mechanisms and libraries to manage concurrency and parallelism in Scala. Some of these are: futures, actors, parallel collections, and the native Java Thread. Scala handles concurrency and parallelism through −</t>
+    <t xml:space="preserve">What are the IDEs that support Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntelliJ IDEA − Comprehensive support for Scala with a dedicated plugin.Visual Studio Code − Lightweight and customizable with Scala plugins.Eclipse − With the Scala IDE plugin.Atom − With Scala plugins for syntax highlighting and code completion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿How does Scala handle concurrency and parallelism?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can use various mechanisms and libraries to manage concurrency and parallelism in Scala. Some of these are: futures, actors, parallel collections, and the native Java Thread. Scala handles concurrency and parallelism through −</t>
   </si>
   <si>
     <t xml:space="preserve">Akka − It uses the actor model to simplify concurrent and distributed programming.Futures and Promises − For handling asynchronous computations and callbacks.Parallel Collections − Allow operations on collections to be executed in parallel.ScalaSTM − It provides software transactional memory for composable and concurrent operations.</t>
@@ -67,71 +79,25 @@
   </si>
   <si>
     <t xml:space="preserve">Immutable data structures.IAn efficient implementation of the equals and hashCode methods.IA copy method to create modified copies.ISupport for pattern matching.IImplements serializable by default.To define a case class, you need the keyword case class, an identifier, and a parameter list, which may be empty. For example −</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is pattern matching in Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattern matching in Scala is a powerful feature. You can match values against patterns and decompose data structures. It is used with case classes and is similar to switch statements in other languages but more powerful and expressive. For example −</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are higher-order functions in Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher-order functions are functions that take other functions as parameters and may return functions as results. These are a key feature of functional programming in Scala. So there can be more abstract and reusable code. For example −</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">What is pattern matching in Scala?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pattern matching</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> in Scala is a powerful feature. You can match values against patterns and decompose data structures. It is used with case classes and is similar to switch statements in other languages but more powerful and expressive. For example −
-</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">What are higher-order functions in Scala?</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Higher-order functions</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> are functions that take other functions as parameters and may return functions as results. These are a key feature of functional programming in Scala. So there can be more abstract and reusable code. For example −</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
@@ -142,6 +108,7 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
@@ -155,6 +122,7 @@
       <rPr>
         <b val="true"/>
         <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
@@ -165,6 +133,7 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
@@ -179,53 +148,31 @@
 Traditional Exception Handling − Using try, catch, and finally blocks.</t>
   </si>
   <si>
+    <t xml:space="preserve">What are traits in Scala?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traits in Scala are similar to interfaces in Java but more powerful. You can define methods and fields that can be reused by multiple classes. Traits can also have concrete methods with implementations. For example −</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are implicit parameters and conversions in Scala?</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">What are traits in Scala?
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Traits in Scala</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> are similar to interfaces in Java but more powerful. You can define methods and fields that can be reused by multiple classes. Traits can also have concrete methods with implementations. For example −
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">What are implicit parameters and conversions in Scala?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="1"/>
@@ -501,43 +448,16 @@
     <t xml:space="preserve">The following list shows the reserved words in Scala. These reserved words may not be used as constant or variable or any other identifier names.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comments in Scala
+    <t xml:space="preserve">Comments in Scala
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Newline Characters
+  </si>
+  <si>
+    <t xml:space="preserve">Newline Characters
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Scala Packages
+  </si>
+  <si>
+    <t xml:space="preserve">Scala Packages
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Apply Dynamic</t>
@@ -546,17 +466,8 @@
     <t xml:space="preserve">A marker trait that enables dynamic invocations. Instances x of this trait allow method invocations x.meth(args) for arbitrary method names meth and argument lists args as well as field accesses x.field for arbitrary field namesfield. This feature is introduced in Scala-2.10. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Hello World Program Code
+    <t xml:space="preserve">Hello World Program Code
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Using a simple function </t>
@@ -577,65 +488,29 @@
     <t xml:space="preserve">These identifiers start with a letter (lowercase or uppercase) or an underscore and followed by digits, letters and underscores. For example, _Name, _name, name123, _1_name_23, name etc. are valid Alphanumeric identifiers. Whereas, 123name, $name, -name etc are invalid identifiers in Scala.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Operator Identifiers
+    <t xml:space="preserve">Operator Identifiers
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">These identifiers contain one or more operator characters. For example, +, ++, :, ?, ~, # etc are Operator identifiers in Scala. The Scala compiler transforms operator identifiers into Java-compatible identifiers. For example, `:-&gt;` becomes `$colon$minus$greater`. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mixed Identifiers
+    <t xml:space="preserve">Mixed Identifiers
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">These identifiers contain alphanumeric identifiers followed by underscore and an operator identifier. For example, sum_ =, unary_+, myvar_=, etc are Mixed identifiers in Scala. In this context, "unary_+" defines an unary plus operator. And "myvar_=" defines an assignment operator, which is a form of operator overloading. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Literal Identifiers
+    <t xml:space="preserve">Literal Identifiers
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">These identifiers contain arbitrary strings enclosed with backticks (`...`). For example, `Name`, `name` etc are Literal identifiers in Scala. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Examples of Scala Identifiers
+    <t xml:space="preserve">Examples of Scala Identifiers
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">For example, below table has valid and invalid identifiers in Scala </t>
@@ -770,16 +645,9 @@
     <t xml:space="preserve">... (Ellipsis)	Used to represent a variable number of arguments in function parameters.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt; (Less Than)	Used in type parameter constraints.
+    <t xml:space="preserve">&lt; (Less Than)	Used in type parameter constraints.
 &gt; (Greater Than)	Used in type parameter constraints.
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve"># (Pound)	Used in context bounds.</t>
@@ -833,17 +701,8 @@
     <t xml:space="preserve">To prevent these problems, we introduce "levels" to count the number of quotes minus the number of splices around an expression and definition. So the system decides what you can and cannot reference.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Conditional Statements
+    <t xml:space="preserve">Conditional Statements
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Loops</t>
@@ -921,17 +780,8 @@
     <t xml:space="preserve">A symbol literal 'x is a shorthand for the expression scala.Symbol("x"). Symbol is a case class, which is defined as follows.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Integral Literals
+    <t xml:space="preserve">Integral Literals
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Integer literals are usually of type Int, or of type Long when followed by a L or l suffix. Here are some integer literals − </t>
@@ -943,33 +793,15 @@
     <t xml:space="preserve">Floating point literals are of type Float when followed by a floating point type suffix F or f, and are of type Double otherwise. Here are some floating point literals −</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Character Literals
+    <t xml:space="preserve">Character Literals
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">A character literal is a single character enclosed in quotes. The character is either a printable Unicode character or is described by an escape sequence. Here are some character literals − </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">String Literals
+    <t xml:space="preserve">String Literals
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">A string literal is a sequence of characters in double quotes. The characters are either printable Unicode character or are described by escape sequences. Here are some string literals − </t>
@@ -1432,17 +1264,8 @@
     <t xml:space="preserve">There can be performance differences between var and val data structures in Scala. The immutable data structures (i.e., val) can have slow performance because you need to copy data structures when changes are made. But there are advantages of immutability too. For example, it is safer and easier-to-maintain code which is usually more important than these drawbacks. We usually use val instead of val in Scala programs because the Scala style prefers immutability, so the code will be more predictable and robust.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Differences between var and val keywords in Scala
+    <t xml:space="preserve">Differences between var and val keywords in Scala
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Arithmetic Operators</t>
@@ -1508,17 +1331,8 @@
     <t xml:space="preserve">1 until 5 creates a range from 1 to 4</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Scala Range Operators (to and until)
+    <t xml:space="preserve">Scala Range Operators (to and until)
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">The range1 is assigned the range 1 to 5. This includes integers from 1 to 5 inclusive. The .toList method converts this range to a list for printing.</t>
@@ -1768,7 +1582,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1791,6 +1605,57 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
@@ -1798,53 +1663,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val=""/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1890,57 +1719,61 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1960,243 +1793,243 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3590640</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>732960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13461480" y="9894960"/>
+          <a:ext cx="3362040" cy="599400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>213480</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>118440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3804120</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1775160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 2" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13446360" y="11004120"/>
+          <a:ext cx="3590640" cy="1656720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>167760</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>88920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4501440</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>916920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13400640" y="13965480"/>
+          <a:ext cx="4333680" cy="828000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152640</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>296640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3717000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1394640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 4" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13385520" y="17988480"/>
+          <a:ext cx="3564360" cy="1098000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>289440</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>325800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4642200</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>2249280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 5" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13522320" y="20165040"/>
+          <a:ext cx="4352760" cy="1923480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3362400</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>599760</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 1" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="8228160"/>
-          <a:ext cx="3362400" cy="599760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:colOff>3614400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>750600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 6" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13232880" y="23694480"/>
+          <a:ext cx="3614400" cy="750600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3591000</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1657080</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 2" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="9352800"/>
-          <a:ext cx="3591000" cy="1657080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4334040</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 3" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="11485800"/>
-          <a:ext cx="4334040" cy="828360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3564720</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1098360</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 4" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="15140880"/>
-          <a:ext cx="3564720" cy="1098360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4353120</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>1923840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 5" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="16675560"/>
-          <a:ext cx="4353120" cy="1923840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3614760</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>750960</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 6" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11995920" y="19558800"/>
-          <a:ext cx="3614760" cy="750960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4457880</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>1076040</xdr:rowOff>
+      <xdr:colOff>4457520</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1075680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2209,32 +2042,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11995920" y="20491560"/>
-          <a:ext cx="4457880" cy="1076040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4105440</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>2761920</xdr:rowOff>
+          <a:off x="13232880" y="24787800"/>
+          <a:ext cx="4457520" cy="1075680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>335520</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>400320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4440600</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>3161880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2247,8 +2080,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11995920" y="29518560"/>
-          <a:ext cx="4105440" cy="2761920"/>
+          <a:off x="13568400" y="36725400"/>
+          <a:ext cx="4105080" cy="2761560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2269,15 +2102,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>243720</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>5088600</xdr:colOff>
+      <xdr:rowOff>176760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5331960</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1035000</xdr:rowOff>
+      <xdr:rowOff>1211400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2290,32 +2123,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="162720"/>
-          <a:ext cx="5088600" cy="1035000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12300480" y="339480"/>
+          <a:ext cx="5088240" cy="1034640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>198000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3568320</xdr:colOff>
+      <xdr:rowOff>103320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3765960</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1845360</xdr:rowOff>
+      <xdr:rowOff>1948320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2328,32 +2161,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="2233800"/>
-          <a:ext cx="3568320" cy="1845360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12254760" y="2369520"/>
+          <a:ext cx="3567960" cy="1845000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>167760</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2964600</xdr:colOff>
+      <xdr:rowOff>235440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3132000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>1613520</xdr:rowOff>
+      <xdr:rowOff>1848600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2366,32 +2199,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="4422600"/>
-          <a:ext cx="2964600" cy="1613520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12224520" y="4980240"/>
+          <a:ext cx="2964240" cy="1613160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2819160</xdr:colOff>
+      <xdr:rowOff>309240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2955960</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1209240</xdr:rowOff>
+      <xdr:rowOff>1518120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2404,32 +2237,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="6555600"/>
-          <a:ext cx="2819160" cy="1209240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12193920" y="7346880"/>
+          <a:ext cx="2818800" cy="1208880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>198000</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2352600</xdr:colOff>
+      <xdr:rowOff>88200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2550240</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>694800</xdr:rowOff>
+      <xdr:rowOff>782640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2442,32 +2275,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="18633600"/>
-          <a:ext cx="2352600" cy="694800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>15840</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>141480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2025360</xdr:colOff>
+          <a:off x="12254760" y="20107800"/>
+          <a:ext cx="2352240" cy="694440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>122400</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>2664720</xdr:rowOff>
+      <xdr:rowOff>52200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2131560</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>2737800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2480,32 +2313,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12071880" y="19989000"/>
-          <a:ext cx="2009520" cy="2685960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12179160" y="21550680"/>
+          <a:ext cx="2009160" cy="2685600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76320</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4152960</xdr:colOff>
+      <xdr:rowOff>103320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4228920</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>1847520</xdr:rowOff>
+      <xdr:rowOff>1950480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2518,32 +2351,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="23532480"/>
-          <a:ext cx="4152960" cy="1847520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="12133080" y="25197120"/>
+          <a:ext cx="4152600" cy="1847160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>487440</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2774160</xdr:colOff>
+      <xdr:rowOff>176760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3261240</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>2836800</xdr:rowOff>
+      <xdr:rowOff>3013200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2556,8 +2389,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="26336160"/>
-          <a:ext cx="2774160" cy="2836800"/>
+          <a:off x="12544200" y="28085760"/>
+          <a:ext cx="2773800" cy="2836440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2579,9 +2412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4448160</xdr:colOff>
+      <xdr:colOff>4447800</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>2419200</xdr:rowOff>
+      <xdr:rowOff>2418840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2594,8 +2427,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="29926800"/>
-          <a:ext cx="4448160" cy="2419200"/>
+          <a:off x="12056760" y="31758840"/>
+          <a:ext cx="4447800" cy="2418840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2617,9 +2450,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2514240</xdr:colOff>
+      <xdr:colOff>2513880</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>685440</xdr:rowOff>
+      <xdr:rowOff>685080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2632,8 +2465,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="32859360"/>
-          <a:ext cx="2514240" cy="685440"/>
+          <a:off x="12056760" y="34691400"/>
+          <a:ext cx="2513880" cy="685080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2655,9 +2488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4152960</xdr:colOff>
+      <xdr:colOff>4152600</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>961560</xdr:rowOff>
+      <xdr:rowOff>961200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2670,8 +2503,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="33940080"/>
-          <a:ext cx="4152960" cy="961560"/>
+          <a:off x="12056760" y="35772120"/>
+          <a:ext cx="4152600" cy="961200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2693,9 +2526,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:colOff>4962240</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>2266560</xdr:rowOff>
+      <xdr:rowOff>2266200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2708,8 +2541,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="36507960"/>
-          <a:ext cx="4962600" cy="2266560"/>
+          <a:off x="12056760" y="38340000"/>
+          <a:ext cx="4962240" cy="2266200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2731,9 +2564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3028680</xdr:colOff>
+      <xdr:colOff>3028320</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>2180880</xdr:rowOff>
+      <xdr:rowOff>2180520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2746,8 +2579,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="39413880"/>
-          <a:ext cx="3028680" cy="2180880"/>
+          <a:off x="12056760" y="41245920"/>
+          <a:ext cx="3028320" cy="2180520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2769,9 +2602,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2695320</xdr:colOff>
+      <xdr:colOff>2694960</xdr:colOff>
       <xdr:row>101</xdr:row>
-      <xdr:rowOff>1190160</xdr:rowOff>
+      <xdr:rowOff>1189800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2784,8 +2617,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="42202800"/>
-          <a:ext cx="2695320" cy="1190160"/>
+          <a:off x="12056760" y="44034840"/>
+          <a:ext cx="2694960" cy="1189800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2807,9 +2640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4600800</xdr:colOff>
+      <xdr:colOff>4600440</xdr:colOff>
       <xdr:row>103</xdr:row>
-      <xdr:rowOff>2228760</xdr:rowOff>
+      <xdr:rowOff>2228400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2822,8 +2655,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="43808760"/>
-          <a:ext cx="4600800" cy="2228760"/>
+          <a:off x="12056760" y="45640800"/>
+          <a:ext cx="4600440" cy="2228400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2845,9 +2678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4276800</xdr:colOff>
+      <xdr:colOff>4276440</xdr:colOff>
       <xdr:row>106</xdr:row>
-      <xdr:rowOff>1819080</xdr:rowOff>
+      <xdr:rowOff>1818720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2860,8 +2693,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12056040" y="46568520"/>
-          <a:ext cx="4276800" cy="1819080"/>
+          <a:off x="12056760" y="48400200"/>
+          <a:ext cx="4276440" cy="1818720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2888,9 +2721,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4286160</xdr:colOff>
+      <xdr:colOff>4285800</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>2228760</xdr:rowOff>
+      <xdr:rowOff>2228400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2904,7 +2737,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13777560" y="1022400"/>
-          <a:ext cx="4286160" cy="2228760"/>
+          <a:ext cx="4285800" cy="2228400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2926,9 +2759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3848040</xdr:colOff>
+      <xdr:colOff>3847680</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>3819600</xdr:rowOff>
+      <xdr:rowOff>3819240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2942,7 +2775,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13777560" y="3855240"/>
-          <a:ext cx="3848040" cy="3819600"/>
+          <a:ext cx="3847680" cy="3819240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2964,9 +2797,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3409920</xdr:colOff>
+      <xdr:colOff>3409560</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1771200</xdr:rowOff>
+      <xdr:rowOff>1770840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2980,7 +2813,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13777560" y="8493120"/>
-          <a:ext cx="3409920" cy="1771200"/>
+          <a:ext cx="3409560" cy="1770840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3002,9 +2835,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3895560</xdr:colOff>
+      <xdr:colOff>3895200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2161800</xdr:rowOff>
+      <xdr:rowOff>2161440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3017,8 +2850,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="11454840"/>
-          <a:ext cx="3895560" cy="2161800"/>
+          <a:off x="13777560" y="11316960"/>
+          <a:ext cx="3895200" cy="2161440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3040,9 +2873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5134320</xdr:colOff>
+      <xdr:colOff>5133960</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>2295360</xdr:rowOff>
+      <xdr:rowOff>2295000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3055,8 +2888,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="14429880"/>
-          <a:ext cx="5134320" cy="2295360"/>
+          <a:off x="13777560" y="14292000"/>
+          <a:ext cx="5133960" cy="2295000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3078,9 +2911,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3838680</xdr:colOff>
+      <xdr:colOff>3838320</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:rowOff>608760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3093,8 +2926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="24286680"/>
-          <a:ext cx="3838680" cy="609120"/>
+          <a:off x="13777560" y="24149160"/>
+          <a:ext cx="3838320" cy="608760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3116,9 +2949,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3181320</xdr:colOff>
+      <xdr:colOff>3180960</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>1247400</xdr:rowOff>
+      <xdr:rowOff>1247040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3131,8 +2964,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="25058880"/>
-          <a:ext cx="3181320" cy="1247400"/>
+          <a:off x="13777560" y="25314840"/>
+          <a:ext cx="3180960" cy="1247040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3154,9 +2987,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4276800</xdr:colOff>
+      <xdr:colOff>4276440</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>761400</xdr:rowOff>
+      <xdr:rowOff>761040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3169,8 +3002,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="26443800"/>
-          <a:ext cx="4276800" cy="761400"/>
+          <a:off x="13777560" y="26699760"/>
+          <a:ext cx="4276440" cy="761040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3192,9 +3025,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4372200</xdr:colOff>
+      <xdr:colOff>4371840</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>656640</xdr:rowOff>
+      <xdr:rowOff>656280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3207,8 +3040,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="27551880"/>
-          <a:ext cx="4372200" cy="656640"/>
+          <a:off x="13777560" y="27807840"/>
+          <a:ext cx="4371840" cy="656280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3230,9 +3063,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4372200</xdr:colOff>
+      <xdr:colOff>4371840</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>1066320</xdr:rowOff>
+      <xdr:rowOff>1065960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3245,8 +3078,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="28266480"/>
-          <a:ext cx="4372200" cy="1066320"/>
+          <a:off x="13777560" y="28522440"/>
+          <a:ext cx="4371840" cy="1065960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3268,9 +3101,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3981600</xdr:colOff>
+      <xdr:colOff>3981240</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>675720</xdr:rowOff>
+      <xdr:rowOff>675360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3283,8 +3116,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="29520000"/>
-          <a:ext cx="3981600" cy="675720"/>
+          <a:off x="13777560" y="29775960"/>
+          <a:ext cx="3981240" cy="675360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3306,9 +3139,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4267080</xdr:colOff>
+      <xdr:colOff>4266720</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>713880</xdr:rowOff>
+      <xdr:rowOff>713520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3321,8 +3154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="30350520"/>
-          <a:ext cx="4267080" cy="713880"/>
+          <a:off x="13777560" y="30606480"/>
+          <a:ext cx="4266720" cy="713520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3344,9 +3177,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4440240</xdr:colOff>
+      <xdr:colOff>4439880</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>1056960</xdr:rowOff>
+      <xdr:rowOff>1056600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3359,8 +3192,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13798080" y="32595120"/>
-          <a:ext cx="4419720" cy="1056960"/>
+          <a:off x="13798080" y="32851080"/>
+          <a:ext cx="4419360" cy="1056600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3382,9 +3215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2904840</xdr:colOff>
+      <xdr:colOff>2904480</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>4257720</xdr:rowOff>
+      <xdr:rowOff>4257360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3397,32 +3230,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="34892640"/>
-          <a:ext cx="2904840" cy="4257720"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="13777560" y="35148600"/>
+          <a:ext cx="2904480" cy="4257360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>213120</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3695760</xdr:colOff>
+      <xdr:rowOff>147240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3908520</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>999720</xdr:rowOff>
+      <xdr:rowOff>1146600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3435,32 +3268,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="41608440"/>
-          <a:ext cx="3695760" cy="999720"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="13990680" y="42011640"/>
+          <a:ext cx="3695400" cy="999360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>198000</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4114800</xdr:colOff>
+      <xdr:rowOff>206280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4312440</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>961560</xdr:rowOff>
+      <xdr:rowOff>1167480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3473,32 +3306,32 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="43566120"/>
-          <a:ext cx="4114800" cy="961560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:off x="13975560" y="44141760"/>
+          <a:ext cx="4114440" cy="961200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>471960</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2800080</xdr:colOff>
+      <xdr:rowOff>309600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3271680</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>1580760</xdr:rowOff>
+      <xdr:rowOff>1890000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3511,8 +3344,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="45331560"/>
-          <a:ext cx="2800080" cy="1580760"/>
+          <a:off x="14249520" y="46387080"/>
+          <a:ext cx="2799720" cy="1580400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3534,9 +3367,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1580760</xdr:colOff>
+      <xdr:colOff>1580400</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>1761840</xdr:rowOff>
+      <xdr:rowOff>1761480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3549,8 +3382,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="47789640"/>
-          <a:ext cx="1580760" cy="1761840"/>
+          <a:off x="13777560" y="48972960"/>
+          <a:ext cx="1580400" cy="1761480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3572,9 +3405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2514240</xdr:colOff>
+      <xdr:colOff>2513880</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>1209240</xdr:rowOff>
+      <xdr:rowOff>1208880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3587,8 +3420,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13777560" y="50036760"/>
-          <a:ext cx="2514240" cy="1209240"/>
+          <a:off x="13777560" y="51220440"/>
+          <a:ext cx="2513880" cy="1208880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3615,9 +3448,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3552840</xdr:colOff>
+      <xdr:colOff>3552480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>933120</xdr:rowOff>
+      <xdr:rowOff>932760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3630,8 +3463,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="3688200"/>
-          <a:ext cx="3552840" cy="933120"/>
+          <a:off x="11814840" y="3553920"/>
+          <a:ext cx="3552480" cy="932760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3653,9 +3486,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1104480</xdr:colOff>
+      <xdr:colOff>1104120</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>1199880</xdr:rowOff>
+      <xdr:rowOff>1199520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3668,8 +3501,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="5427360"/>
-          <a:ext cx="1104480" cy="1199880"/>
+          <a:off x="11814840" y="5304960"/>
+          <a:ext cx="1104120" cy="1199520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3691,9 +3524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>799560</xdr:colOff>
+      <xdr:colOff>799200</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>1180800</xdr:rowOff>
+      <xdr:rowOff>1180440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3706,8 +3539,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="7385040"/>
-          <a:ext cx="799560" cy="1180800"/>
+          <a:off x="11814840" y="7273800"/>
+          <a:ext cx="799200" cy="1180440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3729,9 +3562,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>914040</xdr:colOff>
+      <xdr:colOff>913680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>1009080</xdr:rowOff>
+      <xdr:rowOff>1008720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3744,8 +3577,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="9796680"/>
-          <a:ext cx="914040" cy="1009080"/>
+          <a:off x="11814840" y="9551520"/>
+          <a:ext cx="913680" cy="1008720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3767,9 +3600,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3154320</xdr:colOff>
+      <xdr:colOff>3153960</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>572400</xdr:rowOff>
+      <xdr:rowOff>572040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3782,8 +3615,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11826000" y="11740680"/>
-          <a:ext cx="3143160" cy="570960"/>
+          <a:off x="11826000" y="11624400"/>
+          <a:ext cx="3142800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3805,9 +3638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1915920</xdr:colOff>
+      <xdr:colOff>1915560</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>803880</xdr:rowOff>
+      <xdr:rowOff>803520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3820,8 +3653,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11826000" y="13870800"/>
-          <a:ext cx="1904760" cy="809280"/>
+          <a:off x="11826000" y="13754520"/>
+          <a:ext cx="1904400" cy="808920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3843,9 +3676,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3786480</xdr:colOff>
+      <xdr:colOff>3786120</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>2602800</xdr:rowOff>
+      <xdr:rowOff>2602440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3858,8 +3691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="15989400"/>
-          <a:ext cx="3786480" cy="2602800"/>
+          <a:off x="11814840" y="15873120"/>
+          <a:ext cx="3786120" cy="2602440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3881,9 +3714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2733480</xdr:colOff>
+      <xdr:colOff>2733120</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>780480</xdr:rowOff>
+      <xdr:rowOff>780120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3896,8 +3729,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="19623240"/>
-          <a:ext cx="2733480" cy="780480"/>
+          <a:off x="11814840" y="19617840"/>
+          <a:ext cx="2733120" cy="780120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3919,9 +3752,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3638520</xdr:colOff>
+      <xdr:colOff>3638160</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>790200</xdr:rowOff>
+      <xdr:rowOff>789840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3934,8 +3767,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="23007960"/>
-          <a:ext cx="3638520" cy="790200"/>
+          <a:off x="11814840" y="23264640"/>
+          <a:ext cx="3638160" cy="789840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3957,9 +3790,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3743280</xdr:colOff>
+      <xdr:colOff>3742920</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>590040</xdr:rowOff>
+      <xdr:rowOff>589680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3972,8 +3805,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="25686360"/>
-          <a:ext cx="3743280" cy="590040"/>
+          <a:off x="11814840" y="25836840"/>
+          <a:ext cx="3742920" cy="589680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3995,9 +3828,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2552400</xdr:colOff>
+      <xdr:colOff>2552040</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>590040</xdr:rowOff>
+      <xdr:rowOff>589680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4010,8 +3843,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="27338040"/>
-          <a:ext cx="2552400" cy="590040"/>
+          <a:off x="11814840" y="27488520"/>
+          <a:ext cx="2552040" cy="589680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4033,9 +3866,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3514680</xdr:colOff>
+      <xdr:colOff>3514320</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>799560</xdr:rowOff>
+      <xdr:rowOff>799200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4048,8 +3881,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="28450080"/>
-          <a:ext cx="3514680" cy="799560"/>
+          <a:off x="11814840" y="28600560"/>
+          <a:ext cx="3514320" cy="799200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4071,9 +3904,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3133800</xdr:colOff>
+      <xdr:colOff>3133440</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
+      <xdr:rowOff>828000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4086,8 +3919,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="29923920"/>
-          <a:ext cx="3133800" cy="828360"/>
+          <a:off x="11814840" y="29940120"/>
+          <a:ext cx="3133440" cy="828000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4109,9 +3942,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2266560</xdr:colOff>
+      <xdr:colOff>2266200</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>590040</xdr:rowOff>
+      <xdr:rowOff>589680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4124,8 +3957,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="32932440"/>
-          <a:ext cx="2266560" cy="590040"/>
+          <a:off x="11814840" y="32677200"/>
+          <a:ext cx="2266200" cy="589680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4147,9 +3980,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4305240</xdr:colOff>
+      <xdr:colOff>4304880</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:rowOff>608760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4162,8 +3995,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="33969240"/>
-          <a:ext cx="4305240" cy="609120"/>
+          <a:off x="11814840" y="33714000"/>
+          <a:ext cx="4304880" cy="608760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4185,9 +4018,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1714320</xdr:colOff>
+      <xdr:colOff>1713960</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>799560</xdr:rowOff>
+      <xdr:rowOff>799200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4200,8 +4033,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="35120520"/>
-          <a:ext cx="1714320" cy="799560"/>
+          <a:off x="11814840" y="34731360"/>
+          <a:ext cx="1713960" cy="799200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4223,9 +4056,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2371680</xdr:colOff>
+      <xdr:colOff>2371320</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>875880</xdr:rowOff>
+      <xdr:rowOff>875520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4238,8 +4071,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="36555840"/>
-          <a:ext cx="2371680" cy="875880"/>
+          <a:off x="11814840" y="36166320"/>
+          <a:ext cx="2371320" cy="875520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4261,9 +4094,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4229280</xdr:colOff>
+      <xdr:colOff>4228920</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>627840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4276,8 +4109,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="38571840"/>
-          <a:ext cx="4229280" cy="628200"/>
+          <a:off x="11814840" y="38044800"/>
+          <a:ext cx="4228920" cy="627840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4299,9 +4132,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3200400</xdr:colOff>
+      <xdr:colOff>3200040</xdr:colOff>
       <xdr:row>102</xdr:row>
-      <xdr:rowOff>580680</xdr:rowOff>
+      <xdr:rowOff>580320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4314,8 +4147,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11814840" y="40058280"/>
-          <a:ext cx="3200400" cy="580680"/>
+          <a:off x="11814840" y="39393360"/>
+          <a:ext cx="3200040" cy="580320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4338,13 +4171,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3743280</xdr:colOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3742920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>761760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4357,8 +4190,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="924480"/>
-          <a:ext cx="3743280" cy="628200"/>
+          <a:off x="10819800" y="924480"/>
+          <a:ext cx="3742920" cy="627840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4376,13 +4209,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2361960</xdr:colOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2361600</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>599760</xdr:rowOff>
+      <xdr:rowOff>733320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4395,8 +4228,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="1873800"/>
-          <a:ext cx="2361960" cy="599760"/>
+          <a:off x="10819800" y="1873800"/>
+          <a:ext cx="2361600" cy="599400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4414,13 +4247,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2504880</xdr:colOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2504520</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>637560</xdr:rowOff>
+      <xdr:rowOff>771120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4433,8 +4266,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="2779920"/>
-          <a:ext cx="2504880" cy="637560"/>
+          <a:off x="10819800" y="2779920"/>
+          <a:ext cx="2504520" cy="637200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4452,13 +4285,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2124000</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2123640</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4471,8 +4304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="3773160"/>
-          <a:ext cx="2124000" cy="628200"/>
+          <a:off x="10819800" y="3773160"/>
+          <a:ext cx="2123640" cy="627840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4490,13 +4323,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3600360</xdr:colOff>
+      <xdr:rowOff>134280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3600000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:rowOff>743040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4509,8 +4342,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="6106320"/>
-          <a:ext cx="3600360" cy="609120"/>
+          <a:off x="10819800" y="6106320"/>
+          <a:ext cx="3600000" cy="608760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4528,13 +4361,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2333520</xdr:colOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2333160</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:rowOff>742680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4547,8 +4380,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="7347600"/>
-          <a:ext cx="2333520" cy="609120"/>
+          <a:off x="10819800" y="7347600"/>
+          <a:ext cx="2333160" cy="608760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4566,13 +4399,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2333520</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>590040</xdr:rowOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2333160</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4585,8 +4418,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="8430840"/>
-          <a:ext cx="2333520" cy="590040"/>
+          <a:off x="10819800" y="8430840"/>
+          <a:ext cx="2333160" cy="589680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4604,13 +4437,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1723680</xdr:colOff>
+      <xdr:rowOff>133920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1723320</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>618840</xdr:rowOff>
+      <xdr:rowOff>752400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4623,8 +4456,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="9307800"/>
-          <a:ext cx="1723680" cy="618840"/>
+          <a:off x="10819800" y="9307800"/>
+          <a:ext cx="1723320" cy="618480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4642,13 +4475,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3524040</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>1800000</xdr:rowOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3523680</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>125280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4661,8 +4494,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="12086640"/>
-          <a:ext cx="3524040" cy="1800000"/>
+          <a:off x="10819800" y="12086640"/>
+          <a:ext cx="3523680" cy="1799640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4680,13 +4513,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1819080</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>1437840</xdr:rowOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1818720</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4699,8 +4532,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="14187960"/>
-          <a:ext cx="1819080" cy="1437840"/>
+          <a:off x="10819800" y="14187960"/>
+          <a:ext cx="1818720" cy="1437480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4718,13 +4551,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2685960</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>923400</xdr:rowOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2685600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>108360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4737,8 +4570,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="15953760"/>
-          <a:ext cx="2685960" cy="923400"/>
+          <a:off x="10819800" y="15953760"/>
+          <a:ext cx="2685600" cy="923040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4756,13 +4589,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>811080</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3369960</xdr:colOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3369600</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>2952720</xdr:rowOff>
+      <xdr:rowOff>3216600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4775,8 +4608,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10817280" y="21339720"/>
-          <a:ext cx="3371760" cy="2952720"/>
+          <a:off x="10818000" y="21339720"/>
+          <a:ext cx="3371400" cy="2952360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4794,13 +4627,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3486240</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>771120</xdr:rowOff>
+      <xdr:rowOff>263880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3485880</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>14400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4813,8 +4646,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="26659080"/>
-          <a:ext cx="3486240" cy="771120"/>
+          <a:off x="10819800" y="26659080"/>
+          <a:ext cx="3485880" cy="770760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4832,13 +4665,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2133360</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>618840</xdr:rowOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2133000</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>110520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4851,8 +4684,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="28750320"/>
-          <a:ext cx="2133360" cy="618840"/>
+          <a:off x="10819800" y="28750320"/>
+          <a:ext cx="2133000" cy="618480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4870,13 +4703,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3666960</xdr:colOff>
+      <xdr:rowOff>264240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3666600</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>1047240</xdr:rowOff>
+      <xdr:rowOff>1311120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4889,8 +4722,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="29847600"/>
-          <a:ext cx="3666960" cy="1047240"/>
+          <a:off x="10819800" y="29847600"/>
+          <a:ext cx="3666600" cy="1046880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4908,13 +4741,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2838240</xdr:colOff>
+      <xdr:rowOff>252720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2837880</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
+      <xdr:rowOff>1080720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4927,8 +4760,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="31982400"/>
-          <a:ext cx="2838240" cy="828360"/>
+          <a:off x="10819800" y="31982400"/>
+          <a:ext cx="2837880" cy="828000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4946,13 +4779,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2562120</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>828360</xdr:rowOff>
+      <xdr:rowOff>241200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2561760</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4965,8 +4798,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="33884280"/>
-          <a:ext cx="2562120" cy="828360"/>
+          <a:off x="10819800" y="33884280"/>
+          <a:ext cx="2561760" cy="828000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4984,13 +4817,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4629240</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>1895040</xdr:rowOff>
+      <xdr:rowOff>241200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4628880</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>95040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5003,8 +4836,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="35761320"/>
-          <a:ext cx="4629240" cy="1895040"/>
+          <a:off x="10819800" y="35761320"/>
+          <a:ext cx="4628880" cy="1894680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5022,13 +4855,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3467160</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>2276280</xdr:rowOff>
+      <xdr:rowOff>241560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3466800</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5041,8 +4874,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="38289960"/>
-          <a:ext cx="3467160" cy="2276280"/>
+          <a:off x="10819800" y="38289960"/>
+          <a:ext cx="3466800" cy="2275920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5060,13 +4893,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4067280</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>1866600</xdr:rowOff>
+      <xdr:rowOff>241200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4066920</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>81360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5079,8 +4912,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10819080" y="41285160"/>
-          <a:ext cx="4067280" cy="1866600"/>
+          <a:off x="10819800" y="41285160"/>
+          <a:ext cx="4066920" cy="1866240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5107,9 +4940,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3219480</xdr:colOff>
+      <xdr:colOff>3219120</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1495080</xdr:rowOff>
+      <xdr:rowOff>1494720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5122,8 +4955,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="941760"/>
-          <a:ext cx="3219480" cy="1495080"/>
+          <a:off x="11769120" y="953280"/>
+          <a:ext cx="3219120" cy="1494720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5145,9 +4978,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4010040</xdr:colOff>
+      <xdr:colOff>4009680</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>2154960</xdr:rowOff>
+      <xdr:rowOff>2154600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5160,8 +4993,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="3232080"/>
-          <a:ext cx="4010040" cy="2154960"/>
+          <a:off x="11769120" y="3109680"/>
+          <a:ext cx="4009680" cy="2154600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5183,9 +5016,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3886200</xdr:colOff>
+      <xdr:colOff>3885840</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>5629680</xdr:rowOff>
+      <xdr:rowOff>5629320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5198,8 +5031,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="5994360"/>
-          <a:ext cx="3886200" cy="5629680"/>
+          <a:off x="11769120" y="5871960"/>
+          <a:ext cx="3885840" cy="5629320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5221,9 +5054,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2733480</xdr:colOff>
+      <xdr:colOff>2733120</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>628200</xdr:rowOff>
+      <xdr:rowOff>627840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5236,8 +5069,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="13075920"/>
-          <a:ext cx="2733480" cy="628200"/>
+          <a:off x="11769120" y="12953520"/>
+          <a:ext cx="2733120" cy="627840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5259,9 +5092,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3190680</xdr:colOff>
+      <xdr:colOff>3190320</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>4619880</xdr:rowOff>
+      <xdr:rowOff>4619520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5274,8 +5107,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="14083560"/>
-          <a:ext cx="3190680" cy="4619880"/>
+          <a:off x="11769120" y="13961160"/>
+          <a:ext cx="3190320" cy="4619520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5297,9 +5130,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3695760</xdr:colOff>
+      <xdr:colOff>3695400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>3190680</xdr:rowOff>
+      <xdr:rowOff>3190320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5312,8 +5145,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="19441080"/>
-          <a:ext cx="3695760" cy="3190680"/>
+          <a:off x="11769120" y="19318680"/>
+          <a:ext cx="3695400" cy="3190320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5335,9 +5168,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3000240</xdr:colOff>
+      <xdr:colOff>2999880</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>3771720</xdr:rowOff>
+      <xdr:rowOff>3771360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5350,8 +5183,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="23872320"/>
-          <a:ext cx="3000240" cy="3771720"/>
+          <a:off x="11769120" y="23749560"/>
+          <a:ext cx="2999880" cy="3771360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5373,9 +5206,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4248360</xdr:colOff>
+      <xdr:colOff>4248000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>990360</xdr:rowOff>
+      <xdr:rowOff>990000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5388,8 +5221,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="30441240"/>
-          <a:ext cx="4248360" cy="990360"/>
+          <a:off x="11769120" y="30184560"/>
+          <a:ext cx="4248000" cy="990000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5411,9 +5244,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4181400</xdr:colOff>
+      <xdr:colOff>4181040</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>2447640</xdr:rowOff>
+      <xdr:rowOff>2447280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5426,8 +5259,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="31593240"/>
-          <a:ext cx="4181400" cy="2447640"/>
+          <a:off x="11769120" y="31336560"/>
+          <a:ext cx="4181040" cy="2447280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5449,9 +5282,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1981080</xdr:colOff>
+      <xdr:colOff>1980720</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>1037880</xdr:rowOff>
+      <xdr:rowOff>1037520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5464,8 +5297,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="35676360"/>
-          <a:ext cx="1981080" cy="1037880"/>
+          <a:off x="11769120" y="35431200"/>
+          <a:ext cx="1980720" cy="1037520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5487,9 +5320,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4152240</xdr:colOff>
+      <xdr:colOff>4151880</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>2577600</xdr:rowOff>
+      <xdr:rowOff>2577240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5502,8 +5335,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="36990720"/>
-          <a:ext cx="4152240" cy="2577600"/>
+          <a:off x="11769120" y="36745560"/>
+          <a:ext cx="4151880" cy="2577240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5525,9 +5358,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3753000</xdr:colOff>
+      <xdr:colOff>3752640</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>3085920</xdr:rowOff>
+      <xdr:rowOff>3085560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5540,8 +5373,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="40381560"/>
-          <a:ext cx="3753000" cy="3085920"/>
+          <a:off x="11769120" y="40136400"/>
+          <a:ext cx="3752640" cy="3085560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5563,9 +5396,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7487280</xdr:colOff>
+      <xdr:colOff>7486920</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>837720</xdr:rowOff>
+      <xdr:rowOff>837360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5578,8 +5411,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="44956080"/>
-          <a:ext cx="7487280" cy="837720"/>
+          <a:off x="11769120" y="44710920"/>
+          <a:ext cx="7486920" cy="837360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5601,9 +5434,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3238560</xdr:colOff>
+      <xdr:colOff>3238200</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>647280</xdr:rowOff>
+      <xdr:rowOff>646920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5616,8 +5449,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="47265480"/>
-          <a:ext cx="3238560" cy="647280"/>
+          <a:off x="11769120" y="47031840"/>
+          <a:ext cx="3238200" cy="646920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5639,9 +5472,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5220000</xdr:colOff>
+      <xdr:colOff>5219640</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>2161800</xdr:rowOff>
+      <xdr:rowOff>2161440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5654,8 +5487,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="48698640"/>
-          <a:ext cx="5220000" cy="2161800"/>
+          <a:off x="11769120" y="48465000"/>
+          <a:ext cx="5219640" cy="2161440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5677,9 +5510,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3267000</xdr:colOff>
+      <xdr:colOff>3266640</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>856800</xdr:rowOff>
+      <xdr:rowOff>856440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5692,8 +5525,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="51796440"/>
-          <a:ext cx="3267000" cy="856800"/>
+          <a:off x="11769120" y="51562800"/>
+          <a:ext cx="3266640" cy="856440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5715,9 +5548,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5372280</xdr:colOff>
+      <xdr:colOff>5371920</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>1047240</xdr:rowOff>
+      <xdr:rowOff>1046880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5730,8 +5563,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="55121040"/>
-          <a:ext cx="5372280" cy="1047240"/>
+          <a:off x="11769120" y="54960480"/>
+          <a:ext cx="5371920" cy="1046880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5753,9 +5586,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7258680</xdr:colOff>
+      <xdr:colOff>7258320</xdr:colOff>
       <xdr:row>97</xdr:row>
-      <xdr:rowOff>1076040</xdr:rowOff>
+      <xdr:rowOff>1075680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5768,8 +5601,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="56641320"/>
-          <a:ext cx="7258680" cy="1076040"/>
+          <a:off x="11769120" y="56480760"/>
+          <a:ext cx="7258320" cy="1075680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5791,9 +5624,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6752880</xdr:colOff>
+      <xdr:colOff>6752520</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>4950360</xdr:rowOff>
+      <xdr:rowOff>4950000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5806,8 +5639,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="60242400"/>
-          <a:ext cx="6752880" cy="4950360"/>
+          <a:off x="11769120" y="59948280"/>
+          <a:ext cx="6752520" cy="4950000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5829,9 +5662,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7325640</xdr:colOff>
+      <xdr:colOff>7325280</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>2225520</xdr:rowOff>
+      <xdr:rowOff>2225160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5844,8 +5677,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="65789280"/>
-          <a:ext cx="7325640" cy="2225520"/>
+          <a:off x="11769120" y="65495160"/>
+          <a:ext cx="7325280" cy="2225160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5867,9 +5700,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6701040</xdr:colOff>
+      <xdr:colOff>6700680</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>3117240</xdr:rowOff>
+      <xdr:rowOff>3116880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5882,8 +5715,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="68884920"/>
-          <a:ext cx="6701040" cy="3117240"/>
+          <a:off x="11769120" y="68590800"/>
+          <a:ext cx="6700680" cy="3116880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5905,9 +5738,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6838200</xdr:colOff>
+      <xdr:colOff>6837840</xdr:colOff>
       <xdr:row>118</xdr:row>
-      <xdr:rowOff>2012760</xdr:rowOff>
+      <xdr:rowOff>2012400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5920,8 +5753,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="72871920"/>
-          <a:ext cx="6838200" cy="2012760"/>
+          <a:off x="11769120" y="72577800"/>
+          <a:ext cx="6837840" cy="2012400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5943,9 +5776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7447320</xdr:colOff>
+      <xdr:colOff>7446960</xdr:colOff>
       <xdr:row>123</xdr:row>
-      <xdr:rowOff>1759680</xdr:rowOff>
+      <xdr:rowOff>1759320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5958,8 +5791,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="75753000"/>
-          <a:ext cx="7447320" cy="1759680"/>
+          <a:off x="11769120" y="75458880"/>
+          <a:ext cx="7446960" cy="1759320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5981,9 +5814,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6929640</xdr:colOff>
+      <xdr:colOff>6929280</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>4416480</xdr:rowOff>
+      <xdr:rowOff>4416120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5996,8 +5829,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="78531840"/>
-          <a:ext cx="6929640" cy="4416480"/>
+          <a:off x="11769120" y="78237720"/>
+          <a:ext cx="6929280" cy="4416120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6019,9 +5852,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7370280</xdr:colOff>
+      <xdr:colOff>7369920</xdr:colOff>
       <xdr:row>132</xdr:row>
-      <xdr:rowOff>5803200</xdr:rowOff>
+      <xdr:rowOff>5802840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6034,8 +5867,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="84253680"/>
-          <a:ext cx="7370280" cy="5803200"/>
+          <a:off x="11769120" y="83959560"/>
+          <a:ext cx="7369920" cy="5802840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6057,9 +5890,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6943320</xdr:colOff>
+      <xdr:colOff>6942960</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>4617720</xdr:rowOff>
+      <xdr:rowOff>4617360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6072,8 +5905,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11769120" y="90938520"/>
-          <a:ext cx="6943320" cy="4617720"/>
+          <a:off x="11769120" y="90644400"/>
+          <a:ext cx="6942960" cy="4617360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6095,14 +5928,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4714560</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4714920</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>580680</xdr:rowOff>
+      <xdr:rowOff>568800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6116,31 +5949,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="941760"/>
-          <a:ext cx="4714920" cy="580680"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4714560" cy="580320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4543200</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4543560</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>609120</xdr:rowOff>
+      <xdr:rowOff>597240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6154,31 +5987,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="1966680"/>
-          <a:ext cx="4543560" cy="609120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4543200" cy="608760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>367560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>419760</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>420120</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2409480</xdr:rowOff>
+      <xdr:rowOff>2322000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6192,31 +6025,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="4375080"/>
-          <a:ext cx="6467760" cy="2409480"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="6467400" cy="2409120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3399840</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3400200</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1962000</xdr:rowOff>
+      <xdr:rowOff>1863360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6230,31 +6063,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="7780680"/>
-          <a:ext cx="3400200" cy="1962000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3399840" cy="1961640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3542760</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3543120</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>2361960</xdr:rowOff>
+      <xdr:rowOff>2262960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6268,31 +6101,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="10500840"/>
-          <a:ext cx="3543120" cy="2361960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3542760" cy="2361600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4142880</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4143240</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>3505320</xdr:rowOff>
+      <xdr:rowOff>3406320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6306,31 +6139,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="13685400"/>
-          <a:ext cx="4143240" cy="3505320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4142880" cy="3504960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4571640</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4572000</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>2714400</xdr:rowOff>
+      <xdr:rowOff>2615760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6344,31 +6177,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="17978760"/>
-          <a:ext cx="4572000" cy="2714400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4571640" cy="2714040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4752000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4752360</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>2046960</xdr:rowOff>
+      <xdr:rowOff>1948320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6382,31 +6215,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="21499200"/>
-          <a:ext cx="4752360" cy="2046960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4752000" cy="2046600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3314160</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3314520</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>2609640</xdr:rowOff>
+      <xdr:rowOff>2511000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6420,31 +6253,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="24538320"/>
-          <a:ext cx="3314520" cy="2609640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3314160" cy="2609280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3209400</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3209760</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>2743200</xdr:rowOff>
+      <xdr:rowOff>2644560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6458,31 +6291,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="27927360"/>
-          <a:ext cx="3209760" cy="2743200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3209400" cy="2742840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3514320</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3514680</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>2276280</xdr:rowOff>
+      <xdr:rowOff>2177640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6496,7 +6329,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="31476960"/>
-          <a:ext cx="3514680" cy="2276280"/>
+          <a:ext cx="3514320" cy="2275920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6513,14 +6346,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>16200</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3244680</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3245040</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>2333520</xdr:rowOff>
+      <xdr:rowOff>2234520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6534,31 +6367,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12026520" y="34472160"/>
-          <a:ext cx="3228840" cy="2333520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3228480" cy="2333160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3257280</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3257640</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>2552400</xdr:rowOff>
+      <xdr:rowOff>2453760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6572,31 +6405,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="37628280"/>
-          <a:ext cx="3257640" cy="2552400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3257280" cy="2552040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3542760</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3543120</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>2390400</xdr:rowOff>
+      <xdr:rowOff>2291400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6610,31 +6443,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="41060880"/>
-          <a:ext cx="3543120" cy="2390400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3542760" cy="2390040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3819240</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3819600</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>2504880</xdr:rowOff>
+      <xdr:rowOff>2405880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6648,31 +6481,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="44347680"/>
-          <a:ext cx="3819600" cy="2504880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3819240" cy="2504520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5086080</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>5086440</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>2981160</xdr:rowOff>
+      <xdr:rowOff>2882160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6686,31 +6519,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="47736720"/>
-          <a:ext cx="5086440" cy="2981160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="5086080" cy="2980800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>151920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4390560</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4390920</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>3600360</xdr:rowOff>
+      <xdr:rowOff>3501720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6724,31 +6557,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="51968520"/>
-          <a:ext cx="4390920" cy="3600360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4390560" cy="3600000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3561840</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3562200</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>2743200</xdr:rowOff>
+      <xdr:rowOff>2644560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6762,7 +6595,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="56792520"/>
-          <a:ext cx="3562200" cy="2743200"/>
+          <a:ext cx="3561840" cy="2742840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6780,13 +6613,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>5049360</xdr:colOff>
+      <xdr:rowOff>30600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5049000</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>1072800</xdr:rowOff>
+      <xdr:rowOff>1103040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6800,7 +6633,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="60487560"/>
-          <a:ext cx="5049360" cy="1072800"/>
+          <a:ext cx="5049000" cy="1072440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6818,13 +6651,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4267080</xdr:colOff>
+      <xdr:rowOff>19080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4266720</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>3848040</xdr:rowOff>
+      <xdr:rowOff>3866760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6838,7 +6671,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="62768520"/>
-          <a:ext cx="4267080" cy="3848040"/>
+          <a:ext cx="4266720" cy="3847680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6856,13 +6689,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4353120</xdr:colOff>
+      <xdr:rowOff>19080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4352760</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>1800000</xdr:rowOff>
+      <xdr:rowOff>1818720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6876,7 +6709,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="67499280"/>
-          <a:ext cx="4353120" cy="1800000"/>
+          <a:ext cx="4352760" cy="1799640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6894,13 +6727,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2676240</xdr:colOff>
+      <xdr:rowOff>7560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2675880</xdr:colOff>
       <xdr:row>103</xdr:row>
-      <xdr:rowOff>2381040</xdr:rowOff>
+      <xdr:rowOff>2388240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6914,31 +6747,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="70039800"/>
-          <a:ext cx="2676240" cy="2381040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="2675880" cy="2380680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>158760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3362040</xdr:colOff>
       <xdr:row>106</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3362400</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>4591080</xdr:rowOff>
+      <xdr:rowOff>4586760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6952,31 +6785,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="73132920"/>
-          <a:ext cx="3362400" cy="4591080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3362040" cy="4590720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>158760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3409560</xdr:colOff>
       <xdr:row>110</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3409920</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>2752560</xdr:rowOff>
+      <xdr:rowOff>2748240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6990,31 +6823,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="78519600"/>
-          <a:ext cx="3409920" cy="2752560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="3409560" cy="2752200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>158760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4571640</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4572000</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>4619880</xdr:rowOff>
+      <xdr:rowOff>4615560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7028,31 +6861,31 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="81641880"/>
-          <a:ext cx="4572000" cy="4619880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+          <a:ext cx="4571640" cy="4619520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>158760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3123720</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3124080</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>2771640</xdr:rowOff>
+      <xdr:rowOff>2767680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7066,7 +6899,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="87576840"/>
-          <a:ext cx="3124080" cy="2771640"/>
+          <a:ext cx="3123720" cy="2771280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7084,13 +6917,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>4162320</xdr:colOff>
+      <xdr:rowOff>113760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4161960</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>4886640</xdr:rowOff>
+      <xdr:rowOff>5000040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7104,7 +6937,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12010320" y="92094840"/>
-          <a:ext cx="4162320" cy="4886640"/>
+          <a:ext cx="4161960" cy="4886280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7131,9 +6964,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3800520</xdr:colOff>
+      <xdr:colOff>3800160</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>2171520</xdr:rowOff>
+      <xdr:rowOff>2171160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7146,8 +6979,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11754360" y="487800"/>
-          <a:ext cx="3800520" cy="2171520"/>
+          <a:off x="11755080" y="487800"/>
+          <a:ext cx="3800160" cy="2171160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7169,9 +7002,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4067280</xdr:colOff>
+      <xdr:colOff>4066920</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>2743200</xdr:rowOff>
+      <xdr:rowOff>2742840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7184,8 +7017,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11754360" y="4065840"/>
-          <a:ext cx="4067280" cy="2743200"/>
+          <a:off x="11755080" y="4065840"/>
+          <a:ext cx="4066920" cy="2742840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7207,9 +7040,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3933720</xdr:colOff>
+      <xdr:colOff>3933360</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2133360</xdr:rowOff>
+      <xdr:rowOff>2133000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7222,8 +7055,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11754360" y="7867800"/>
-          <a:ext cx="3933720" cy="2133360"/>
+          <a:off x="11755080" y="7867800"/>
+          <a:ext cx="3933360" cy="2133000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7245,9 +7078,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4076640</xdr:colOff>
+      <xdr:colOff>4076280</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>2943000</xdr:rowOff>
+      <xdr:rowOff>2942640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7260,8 +7093,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11754360" y="11331000"/>
-          <a:ext cx="4076640" cy="2943000"/>
+          <a:off x="11755080" y="11331000"/>
+          <a:ext cx="4076280" cy="2942640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7388,355 +7221,379 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A98"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="89.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="68.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="107.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="68.49"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="32.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="32.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="63.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="63.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
+      <c r="A4" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="58.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="57.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="58.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="57.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+    </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="35.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="45.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="142.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>13</v>
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="45.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="83.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="146.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="72.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="67.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="23" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="163" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="73.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+    <row r="25" customFormat="false" ht="96.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="96.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+    <row r="27" customFormat="false" ht="72.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+    <row r="31" customFormat="false" ht="67.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+    <row r="33" customFormat="false" ht="143.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+    <row r="36" customFormat="false" ht="195.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="37" customFormat="false" ht="48.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="21.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="86.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="105.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
+      <c r="A46" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>25</v>
+      <c r="A47" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
+      <c r="A48" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>26</v>
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="30.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="A51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="22.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="30.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>30</v>
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="36.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" customFormat="false" ht="17.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="37.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
+      <c r="A61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
+      <c r="A62" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="A64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
-        <v>35</v>
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="17.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="45.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="A69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
+      <c r="A70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>38</v>
+      <c r="A71" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="A73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>40</v>
+      <c r="A74" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>41</v>
+      <c r="A75" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>42</v>
+      <c r="A76" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>43</v>
+      <c r="A77" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
-        <v>44</v>
+      <c r="A78" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
-        <v>45</v>
+      <c r="A80" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>46</v>
+      <c r="A81" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="A82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
+      <c r="A83" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>48</v>
+      <c r="A84" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>49</v>
+      <c r="A85" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="229.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="106.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="53.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0"/>
-    </row>
-    <row r="95" customFormat="false" ht="388.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0"/>
-    </row>
+      <c r="A86" s="3"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="274.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="106.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="53.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A19" r:id="rId1" display="Pattern matching"/>
-    <hyperlink ref="A22" r:id="rId2" display="Higher-order functions"/>
-    <hyperlink ref="A33" r:id="rId3" display="Traits in Scala"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7744,7 +7601,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7756,373 +7613,376 @@
   <dimension ref="A2:A107"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="90.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="73.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="90.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="93.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="113.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="159.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="169.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="142.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="68.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="154.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="144.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="76.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>62</v>
+      <c r="A16" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>78</v>
+      <c r="A33" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>79</v>
+      <c r="A34" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>80</v>
+      <c r="A35" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>81</v>
+      <c r="A36" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>82</v>
+      <c r="A37" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>83</v>
+      <c r="A38" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>84</v>
+      <c r="A39" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>85</v>
+      <c r="A43" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>86</v>
+      <c r="A44" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>87</v>
+      <c r="A45" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>88</v>
+      <c r="A46" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>89</v>
+      <c r="A47" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>90</v>
+      <c r="A48" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>91</v>
+      <c r="A49" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>87</v>
+      <c r="A56" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>88</v>
+      <c r="A57" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>89</v>
+      <c r="A58" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>90</v>
+      <c r="A59" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>91</v>
+      <c r="A60" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>92</v>
+      <c r="A61" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>93</v>
+      <c r="A62" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>94</v>
+      <c r="A64" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>95</v>
+      <c r="A65" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>96</v>
+      <c r="A66" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>97</v>
+      <c r="A67" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>98</v>
+      <c r="A68" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="70" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>100</v>
+      <c r="A69" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="78.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="226.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>102</v>
+      <c r="A73" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="231.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>103</v>
+      <c r="A77" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="172.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="234.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>107</v>
+      <c r="A81" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="253.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="s">
-        <v>108</v>
+      <c r="A89" s="10" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="72.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8" t="s">
-        <v>109</v>
+      <c r="A91" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="90.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="8" t="s">
-        <v>110</v>
+      <c r="A93" s="10" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="98.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="9" t="s">
-        <v>111</v>
+      <c r="A95" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="203.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="194" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
-        <v>113</v>
+      <c r="A99" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="113.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="s">
-        <v>114</v>
+      <c r="A102" s="9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="191.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
-        <v>115</v>
+      <c r="A104" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
-        <v>116</v>
+      <c r="A105" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="166.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
-        <v>117</v>
+      <c r="A107" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8145,409 +8005,411 @@
   <dimension ref="A2:A109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="86.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="39.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="85.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="86.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="85.4"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="67.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>118</v>
+      <c r="A2" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="197.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>119</v>
+      <c r="A3" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="315.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>120</v>
+      <c r="A6" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="36.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>121</v>
+      <c r="A7" s="8" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="174.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>123</v>
+      <c r="A9" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="184.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>124</v>
+      <c r="A12" s="11" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>126</v>
+      <c r="A16" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>127</v>
+      <c r="A17" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>128</v>
+      <c r="A20" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>129</v>
+      <c r="A21" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>130</v>
+      <c r="A22" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>131</v>
+      <c r="A23" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>132</v>
+      <c r="A24" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>133</v>
+      <c r="A25" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>134</v>
+      <c r="A26" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>135</v>
+      <c r="A27" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>136</v>
+      <c r="A28" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>137</v>
+      <c r="A29" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>138</v>
+      <c r="A30" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>139</v>
+      <c r="A31" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>140</v>
+      <c r="A32" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>141</v>
+      <c r="A33" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>142</v>
+      <c r="A34" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>143</v>
+      <c r="A35" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>144</v>
+      <c r="A36" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>145</v>
+      <c r="A37" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>146</v>
+      <c r="A38" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>147</v>
+      <c r="A39" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>148</v>
+      <c r="A40" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>149</v>
+      <c r="A41" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>150</v>
+      <c r="A42" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>151</v>
+      <c r="A43" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>152</v>
+      <c r="A44" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>153</v>
+      <c r="A45" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>154</v>
+      <c r="A46" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>155</v>
+      <c r="A47" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>156</v>
+      <c r="A48" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>157</v>
+      <c r="A49" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>158</v>
+      <c r="A50" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>159</v>
+      <c r="A51" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>160</v>
+      <c r="A52" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>161</v>
+      <c r="A53" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>162</v>
+      <c r="A54" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>163</v>
+      <c r="A55" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="60.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>165</v>
+      <c r="A58" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="91.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="109.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>166</v>
+      <c r="A60" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="87.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>167</v>
+      <c r="A61" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>168</v>
+      <c r="A62" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="98.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>169</v>
+      <c r="A63" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="65.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>170</v>
+      <c r="A64" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="76.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="s">
-        <v>171</v>
+      <c r="A65" s="12" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="99.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>172</v>
+      <c r="A66" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="129.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>173</v>
+      <c r="A67" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="353.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>174</v>
+      <c r="A72" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>175</v>
+      <c r="A73" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>176</v>
+      <c r="A74" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>177</v>
+      <c r="A75" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>178</v>
+      <c r="A76" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>179</v>
+      <c r="A77" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>180</v>
+      <c r="A78" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>181</v>
+      <c r="A79" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>182</v>
+      <c r="A80" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>183</v>
+      <c r="A83" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="105.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="91.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="142.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8" t="s">
-        <v>189</v>
+      <c r="A84" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="113.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="176.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="10" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>190</v>
+      <c r="A96" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="164.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="114.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="s">
-        <v>192</v>
+      <c r="A97" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="145.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="42.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="37.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -8570,391 +8432,393 @@
   <dimension ref="A2:A127"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="86.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="66.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="86.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="66.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>198</v>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>199</v>
+      <c r="A4" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>200</v>
+      <c r="A5" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>201</v>
+      <c r="A6" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>202</v>
+      <c r="A7" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>203</v>
+      <c r="A8" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>204</v>
+      <c r="A9" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>205</v>
+      <c r="A10" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>206</v>
+      <c r="A11" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>207</v>
+      <c r="A12" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>208</v>
+      <c r="A13" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>209</v>
+      <c r="A14" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>210</v>
+      <c r="A15" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>211</v>
+      <c r="A16" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>212</v>
+      <c r="A17" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="88.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>214</v>
+      <c r="A22" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="105.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>216</v>
+      <c r="A26" s="11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="117.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="92.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>220</v>
+      <c r="A30" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="113.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="60.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>221</v>
+      <c r="A39" s="5" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>222</v>
+      <c r="A40" s="8" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="92.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>223</v>
+      <c r="A45" s="5" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="214.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="72.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="234.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="92.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="91.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>228</v>
+      <c r="A55" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>229</v>
+      <c r="A56" s="1" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>230</v>
+      <c r="A57" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>231</v>
+      <c r="A58" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>232</v>
+      <c r="A59" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="78.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>235</v>
+      <c r="A60" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="90.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>237</v>
+      <c r="A68" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="53.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>238</v>
+      <c r="A72" s="6" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="50.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>239</v>
+      <c r="A73" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>240</v>
+      <c r="A76" s="3" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="68.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
-        <v>242</v>
+      <c r="A79" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="82.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>244</v>
+      <c r="A82" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="s">
-        <v>246</v>
+      <c r="A86" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="68.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="s">
-        <v>247</v>
+      <c r="A89" s="8" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
-        <v>249</v>
+      <c r="A91" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="s">
-        <v>250</v>
+      <c r="A93" s="9" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="87.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>252</v>
+      <c r="A97" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
+      <c r="A99" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="71.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
-        <v>254</v>
+      <c r="A101" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="71.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
-        <v>255</v>
+      <c r="A103" s="9" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>256</v>
+      <c r="A106" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
-        <v>257</v>
+      <c r="A107" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
+      <c r="A108" s="3"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2"/>
+      <c r="A109" s="3"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>259</v>
+      <c r="A110" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2"/>
+      <c r="A112" s="3"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>261</v>
+      <c r="A113" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2"/>
+      <c r="A115" s="3"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
-        <v>263</v>
+      <c r="A116" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>264</v>
+      <c r="A120" s="3" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>265</v>
+      <c r="A121" s="3" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2"/>
+      <c r="A122" s="3"/>
     </row>
     <row r="123" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
-        <v>266</v>
+      <c r="A123" s="3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
-        <v>268</v>
+      <c r="A124" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
-        <v>270</v>
+      <c r="A126" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -8977,228 +8841,230 @@
   <dimension ref="A2:A85"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="72.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="107.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="72.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="107.44"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>272</v>
+      <c r="A2" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>273</v>
+      <c r="A5" s="9" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="58.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>274</v>
+      <c r="A7" s="9" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="65.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>275</v>
+      <c r="A9" s="9" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>276</v>
+      <c r="A11" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>277</v>
+      <c r="A18" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>278</v>
+      <c r="A19" s="3" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="84.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>279</v>
+      <c r="A20" s="9" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>280</v>
+      <c r="A22" s="8" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>281</v>
+      <c r="A25" s="8" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="87.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>283</v>
+      <c r="A27" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>285</v>
+      <c r="A31" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="152.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>286</v>
+      <c r="A34" s="9" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="126.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>287</v>
+      <c r="A36" s="9" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="84.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>288</v>
+      <c r="A38" s="9" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="243.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>260</v>
+      <c r="A41" s="3" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>289</v>
+      <c r="A42" s="3" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="253.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>290</v>
+      <c r="A44" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>291</v>
+      <c r="A48" s="3" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>292</v>
+      <c r="A49" s="3" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="42.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>293</v>
+      <c r="A52" s="3" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="80.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>294</v>
+      <c r="A53" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>295</v>
+      <c r="A54" s="3" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>296</v>
+      <c r="A57" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="60.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>297</v>
+      <c r="A58" s="3" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>298</v>
+      <c r="A60" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="106.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
-        <v>300</v>
+      <c r="A61" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>301</v>
+      <c r="A65" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="88.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
-        <v>303</v>
+      <c r="A66" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
-        <v>304</v>
+      <c r="A70" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="83.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>305</v>
+      <c r="A71" s="3" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>306</v>
+      <c r="A72" s="3" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>307</v>
+      <c r="A75" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>308</v>
+      <c r="A76" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="160.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>309</v>
+      <c r="A77" s="3" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>310</v>
+      <c r="A80" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="197.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
-        <v>311</v>
+      <c r="A81" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>312</v>
+      <c r="A84" s="3" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="159.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>313</v>
+      <c r="A85" s="3" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -9221,394 +9087,396 @@
   <dimension ref="A3:A137"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="86.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="108.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="86.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="108.95"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>315</v>
+      <c r="A3" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="133.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>317</v>
+      <c r="A6" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="179.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>318</v>
+      <c r="A9" s="8" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>319</v>
+      <c r="A12" s="3" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="459.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>320</v>
+      <c r="A13" s="3" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>321</v>
+      <c r="A14" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>322</v>
+      <c r="A17" s="3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>323</v>
+      <c r="A18" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="66.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>324</v>
+      <c r="A20" s="1" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>325</v>
+      <c r="A21" s="1" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="383.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>326</v>
+      <c r="A22" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>327</v>
+      <c r="A25" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="272.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>328</v>
+      <c r="A26" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>329</v>
+      <c r="A32" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="307.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>331</v>
+      <c r="A33" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>332</v>
+      <c r="A35" s="3" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>333</v>
+      <c r="A39" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>334</v>
+      <c r="A40" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>335</v>
+      <c r="A41" s="1" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>336</v>
+      <c r="A42" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>337</v>
+      <c r="A43" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>338</v>
+      <c r="A46" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="90.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>339</v>
+      <c r="A47" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>342</v>
+      <c r="A54" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
+      <c r="A56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="90.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>343</v>
+      <c r="A57" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
-        <v>344</v>
+      <c r="A59" s="9" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>345</v>
+      <c r="A60" s="9" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
-        <v>346</v>
+      <c r="A63" s="3" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="262.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>347</v>
+      <c r="A64" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>350</v>
+      <c r="A69" s="3" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="83.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
-        <v>351</v>
+      <c r="A70" s="3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="36.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
-        <v>352</v>
+      <c r="A71" s="8" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>354</v>
+      <c r="A74" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="87.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>355</v>
+      <c r="A76" s="3" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="198.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="s">
-        <v>358</v>
+      <c r="A80" s="9" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="74.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="80.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>361</v>
+      <c r="A87" s="5" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="11" t="s">
-        <v>363</v>
+      <c r="A89" s="6" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11" t="s">
-        <v>364</v>
+      <c r="A90" s="6" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="s">
-        <v>365</v>
+      <c r="A91" s="6" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
-        <v>366</v>
+      <c r="A94" s="3" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="94.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>367</v>
+      <c r="A95" s="3" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>368</v>
+      <c r="A97" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="102.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>369</v>
+      <c r="A98" s="3" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
-        <v>370</v>
+      <c r="A99" s="3" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
-        <v>372</v>
+      <c r="A100" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="68.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
-        <v>374</v>
+      <c r="A104" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="398.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="8" t="s">
-        <v>375</v>
+      <c r="A108" s="13" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
-        <v>376</v>
+      <c r="A111" s="1" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="211.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
-        <v>377</v>
+      <c r="A112" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="8" t="s">
-        <v>378</v>
+      <c r="A114" s="10" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="268.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="8" t="s">
-        <v>380</v>
+      <c r="A118" s="10" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="175.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
-        <v>382</v>
+      <c r="A123" s="1" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="160.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>383</v>
+      <c r="A124" s="3" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="8" t="s">
-        <v>384</v>
+      <c r="A128" s="10" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="405.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="8" t="s">
-        <v>386</v>
+      <c r="A132" s="10" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="481.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="8" t="s">
-        <v>388</v>
+      <c r="A136" s="10" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="454.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -9631,353 +9499,355 @@
   <dimension ref="A2:A130"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="89.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="74.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="89.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="74.27"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>391</v>
+      <c r="A2" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>392</v>
+      <c r="A5" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>393</v>
+      <c r="A6" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>394</v>
+      <c r="A7" s="1" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>395</v>
+      <c r="A9" s="1" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>397</v>
+      <c r="A10" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="194" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>399</v>
+      <c r="A19" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>400</v>
+      <c r="A24" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="163" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>401</v>
+      <c r="A25" s="1" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>402</v>
+      <c r="A29" s="3" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="212.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>403</v>
+      <c r="A30" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>404</v>
+      <c r="A33" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="299.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>405</v>
+      <c r="A34" s="3" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>406</v>
+      <c r="A37" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="231.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>407</v>
+      <c r="A38" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>408</v>
+      <c r="A41" s="10" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="194" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>410</v>
+      <c r="A45" s="10" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="221.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
-        <v>412</v>
+      <c r="A49" s="10" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="234.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>414</v>
+      <c r="A53" s="10" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="190.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
-        <v>416</v>
+      <c r="A57" s="10" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="210.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>418</v>
+      <c r="A61" s="3" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>419</v>
+      <c r="A62" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8" t="s">
-        <v>420</v>
+      <c r="A65" s="10" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="213.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="8" t="s">
-        <v>422</v>
+      <c r="A69" s="10" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="221.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>424</v>
+      <c r="A73" s="10" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="264.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="11" t="s">
-        <v>426</v>
+      <c r="A75" s="6" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8" t="s">
-        <v>427</v>
+      <c r="A78" s="10" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="303.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>429</v>
+      <c r="A83" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>430</v>
+      <c r="A84" s="1" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>431</v>
+      <c r="A85" s="1" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="229.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="s">
-        <v>433</v>
+      <c r="A86" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
-        <v>434</v>
+      <c r="A90" s="1" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="118.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
-        <v>436</v>
+      <c r="A91" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>437</v>
+      <c r="A95" s="3" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="327.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
-        <v>438</v>
+      <c r="A96" s="3" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8" t="s">
-        <v>439</v>
+      <c r="A99" s="10" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
-        <v>441</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>442</v>
+      <c r="A103" s="3" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="207.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
-        <v>444</v>
+      <c r="A104" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="385.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="s">
-        <v>445</v>
+      <c r="A107" s="8" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>446</v>
+      <c r="A110" s="3" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="233.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>447</v>
+      <c r="A111" s="3" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="377.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="s">
-        <v>448</v>
+      <c r="A113" s="8" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="s">
-        <v>449</v>
+      <c r="A114" s="9" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>450</v>
+      <c r="A120" s="3" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="233.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>452</v>
+      <c r="A121" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="3" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>453</v>
+      <c r="A124" s="3" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
-        <v>454</v>
+      <c r="A125" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
-        <v>456</v>
+      <c r="A126" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
-        <v>457</v>
+      <c r="A129" s="3" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="396.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
-        <v>458</v>
+      <c r="A130" s="3" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -10000,93 +9870,95 @@
   <dimension ref="A2:A25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="86.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="66.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="86.06"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="66.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>459</v>
+      <c r="A2" s="3" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>460</v>
+      <c r="A3" s="3" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="197.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>461</v>
+      <c r="A4" s="3" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>462</v>
+      <c r="A5" s="3" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>463</v>
+      <c r="A8" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="235.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>464</v>
+      <c r="A9" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>465</v>
+      <c r="A10" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>466</v>
+      <c r="A14" s="3" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="187.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>467</v>
+      <c r="A15" s="3" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>468</v>
+      <c r="A16" s="3" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>469</v>
+      <c r="A19" s="3" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>470</v>
+      <c r="A20" s="3" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="246.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>471</v>
+      <c r="A21" s="3" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>472</v>
+      <c r="A22" s="1" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>473</v>
+      <c r="A23" s="1" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>474</v>
+      <c r="A24" s="1" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>475</v>
+      <c r="A25" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -10109,17 +9981,19 @@
   <dimension ref="B3:B7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="63.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="63.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>476</v>
+      <c r="B3" s="1" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>477</v>
+      <c r="B7" s="1" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>
